--- a/business_forms/018_corporate_csr_event_request_form--business_forms.xlsx
+++ b/business_forms/018_corporate_csr_event_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>csrrequestformnote</t>
+          <t>Corporatecsrrequestform9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>Corporatecsrrequestform11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Corporatecsrrequestform12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Corporatecsrrequestform13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>Corporatecsrrequestform14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Corporatecsrrequestform15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>Corporatecsrrequestform16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Corporatecsrrequestform17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -932,7 +932,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Corporatecsrrequestform18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>corporatecsrrequestformtitle</t>
+          <t>Corporatecsrrequestform21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,8 +1026,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'option6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option7'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'option7'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'option8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'option8'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'option9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'option9'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option10'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'option10'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'option11'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'option11'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'option12'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'option12'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'option13'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'option13'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'option14'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'option14'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'option15'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'option15'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'option16'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'option16'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'option17'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'option17'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'option18'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'option18'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'option19'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'option19'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'option20'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'option20'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'option21'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'option21'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'option22'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'option22'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'option23'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'option23'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'option24'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'option24'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'option25'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'option25'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'option26'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'option26'}</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'option27'}</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'option27'}</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'option28'}</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'option28'}</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'option29'}</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'option29'}</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'option30'}</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'option30'}</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
